--- a/schemas/ldac/schema-crate/ro-crate-metadata.xlsx
+++ b/schemas/ldac/schema-crate/ro-crate-metadata.xlsx
@@ -233,12 +233,21 @@
     <t>inDefinedTermSet</t>
   </si>
   <si>
+    <t>https://w3id.org/ro/mode</t>
+  </si>
+  <si>
+    <t>DefinedTerm</t>
+  </si>
+  <si>
+    <t>Editor Mode</t>
+  </si>
+  <si>
+    <t>Role indicating a resource is an editor configuration mode file.</t>
+  </si>
+  <si>
     <t>https://w3id.org/ldac/terms#TimeAligned</t>
   </si>
   <si>
-    <t>DefinedTerm</t>
-  </si>
-  <si>
     <t>TimeAligned</t>
   </si>
   <si>
@@ -647,6 +656,96 @@
     <t>The resource contains data for which the medium of interaction was writing.</t>
   </si>
   <si>
+    <t>https://w3id.org/ldac/terms#AuthorizedAccess</t>
+  </si>
+  <si>
+    <t>AuthorizedAccess</t>
+  </si>
+  <si>
+    <t>Indicates that a DataReuseLicense requires some kind of authorization step, from SelfAuthorization (click-through) to processes that require a data steward to grant permission.</t>
+  </si>
+  <si>
+    <t>"https://w3id.org/ldac/terms#AccessTypes"</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#OpenAccess</t>
+  </si>
+  <si>
+    <t>OpenAccess</t>
+  </si>
+  <si>
+    <t>Data covered by this license may be accessed as long as the license is served alongside it, and does not require any specific authorization step.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#Gestural</t>
+  </si>
+  <si>
+    <t>Gestural</t>
+  </si>
+  <si>
+    <t>The resource describes the gestural content of the resource it annotates.</t>
+  </si>
+  <si>
+    <t>"http://www.language-archives.org/REC/type-20020628.html#description/gestural"</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#AgreeToTerms</t>
+  </si>
+  <si>
+    <t>AgreeToTerms</t>
+  </si>
+  <si>
+    <t>A user is expected to explicitly agree to a set of license terms, this may be combined with AccessControlList - to note that even if a user has been pre-approved for a license they must agree to license terms.</t>
+  </si>
+  <si>
+    <t>"https://w3id.org/ldac/terms#AuthorizationWorkflows"</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#AuthorizationByApplication</t>
+  </si>
+  <si>
+    <t>AuthorizationByApplication</t>
+  </si>
+  <si>
+    <t>Users may apply for a license via some workflow, such as a form, with the decision being made by a DataSteward or their delegate about whether to grant the license.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#AuthorizationByInvitation</t>
+  </si>
+  <si>
+    <t>AuthorizationByInvitation</t>
+  </si>
+  <si>
+    <t>A data steward or administrator is expected to use an access control system to invite users, for example, participants, collaborators or students.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#SelfAuthorization</t>
+  </si>
+  <si>
+    <t>SelfAuthorization</t>
+  </si>
+  <si>
+    <t>A user can be authorised to access data by clicking that they agree to a license, or filling out a form to check their understanding, which can be validated by a machine and does not require human intervention.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#AccessControlList</t>
+  </si>
+  <si>
+    <t>AccessControlList</t>
+  </si>
+  <si>
+    <t>License grants access to data based on a list of approved users, specified using the property accessControlList.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/ldac/terms#WhistledLanguage</t>
+  </si>
+  <si>
+    <t>WhistledLanguage</t>
+  </si>
+  <si>
+    <t>The resource contains data for which the medium of interaction was whistling.</t>
+  </si>
+  <si>
     <t>https://w3id.org/ldac/terms#FullText</t>
   </si>
   <si>
@@ -659,15 +758,6 @@
     <t>"https://w3id.org/ldac/terms#IndexTypes"</t>
   </si>
   <si>
-    <t>https://w3id.org/ldac/terms#WhistledLanguage</t>
-  </si>
-  <si>
-    <t>WhistledLanguage</t>
-  </si>
-  <si>
-    <t>The resource contains data for which the medium of interaction was whistling.</t>
-  </si>
-  <si>
     <t>https://w3id.org/ldac/terms#Oratory</t>
   </si>
   <si>
@@ -678,96 +768,6 @@
   </si>
   <si>
     <t>"http://www.language-archives.org/REC/type-20020628.html#text/oratory"</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#Gestural</t>
-  </si>
-  <si>
-    <t>Gestural</t>
-  </si>
-  <si>
-    <t>The resource describes the gestural content of the resource it annotates.</t>
-  </si>
-  <si>
-    <t>"http://www.language-archives.org/REC/type-20020628.html#description/gestural"</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#AgreeToTerms</t>
-  </si>
-  <si>
-    <t>AgreeToTerms</t>
-  </si>
-  <si>
-    <t>A user is expected to explicitly agree to a set of license terms, this may be combined with AccessControlList - to note that even if a user has been pre-approved for a license they must agree to license terms.</t>
-  </si>
-  <si>
-    <t>"https://w3id.org/ldac/terms#AuthorizationWorkflows"</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#AuthorizationByApplication</t>
-  </si>
-  <si>
-    <t>AuthorizationByApplication</t>
-  </si>
-  <si>
-    <t>Users may apply for a license via some workflow, such as a form, with the decision being made by a DataSteward or their delegate about whether to grant the license.</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#AuthorizationByInvitation</t>
-  </si>
-  <si>
-    <t>AuthorizationByInvitation</t>
-  </si>
-  <si>
-    <t>A data steward or administrator is expected to use an access control system to invite users, for example, participants, collaborators or students.</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#SelfAuthorization</t>
-  </si>
-  <si>
-    <t>SelfAuthorization</t>
-  </si>
-  <si>
-    <t>A user can be authorised to access data by clicking that they agree to a license, or filling out a form to check their understanding, which can be validated by a machine and does not require human intervention.</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#AccessControlList</t>
-  </si>
-  <si>
-    <t>AccessControlList</t>
-  </si>
-  <si>
-    <t>License grants access to data based on a list of approved users, specified using the property accessControlList.</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#AuthorizedAccess</t>
-  </si>
-  <si>
-    <t>AuthorizedAccess</t>
-  </si>
-  <si>
-    <t>Indicates that a DataReuseLicense requires some kind of authorization step, from SelfAuthorization (click-through) to processes that require a data steward to grant permission.</t>
-  </si>
-  <si>
-    <t>"https://w3id.org/ldac/terms#AccessTypes"</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ldac/terms#OpenAccess</t>
-  </si>
-  <si>
-    <t>OpenAccess</t>
-  </si>
-  <si>
-    <t>Data covered by this license may be accessed as long as the license is served alongside it, and does not require any specific authorization step.</t>
-  </si>
-  <si>
-    <t>https://w3id.org/ro/mode</t>
-  </si>
-  <si>
-    <t>Editor Mode</t>
-  </si>
-  <si>
-    <t>Role indicating a resource is an editor configuration mode file.</t>
   </si>
   <si>
     <t>hasDefinedTerm</t>
@@ -2515,10 +2515,10 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
         <v>67</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
       </c>
       <c r="F1" t="s">
         <v>68</v>
@@ -2547,7 +2547,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -2560,162 +2560,159 @@
       <c r="E3" t="s">
         <v>76</v>
       </c>
-      <c r="F3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" t="s">
         <v>80</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
         <v>81</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>82</v>
-      </c>
-      <c r="G4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
         <v>84</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>85</v>
       </c>
-      <c r="I5" t="s">
-        <v>86</v>
+      <c r="G5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
         <v>88</v>
       </c>
-      <c r="E6" t="s">
+      <c r="I6" t="s">
         <v>89</v>
-      </c>
-      <c r="F6" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
         <v>92</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>93</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" t="s">
         <v>96</v>
       </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
         <v>97</v>
-      </c>
-      <c r="F8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" t="s">
         <v>100</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>101</v>
       </c>
       <c r="I9" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
         <v>104</v>
       </c>
-      <c r="E10" t="s">
+      <c r="I10" t="s">
         <v>105</v>
-      </c>
-      <c r="I10" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
         <v>108</v>
       </c>
-      <c r="E11" t="s">
+      <c r="I11" t="s">
         <v>109</v>
-      </c>
-      <c r="I11" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2728,11 +2725,11 @@
       <c r="C12" t="s">
         <v>111</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D12" t="s">
         <v>112</v>
       </c>
       <c r="I12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2745,180 +2742,174 @@
       <c r="C13" t="s">
         <v>114</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D13" t="s">
         <v>115</v>
       </c>
-      <c r="F13" t="s">
-        <v>116</v>
-      </c>
       <c r="I13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
         <v>118</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>119</v>
       </c>
-      <c r="F14" t="s">
-        <v>120</v>
-      </c>
       <c r="I14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" t="s">
         <v>122</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>123</v>
       </c>
-      <c r="F15" t="s">
-        <v>124</v>
-      </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" t="s">
         <v>126</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>127</v>
       </c>
-      <c r="F16" t="s">
-        <v>128</v>
-      </c>
       <c r="I16" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" t="s">
         <v>131</v>
       </c>
-      <c r="E17" t="s">
+      <c r="I17" t="s">
         <v>132</v>
-      </c>
-      <c r="F17" t="s">
-        <v>133</v>
-      </c>
-      <c r="I17" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" t="s">
         <v>135</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>136</v>
       </c>
-      <c r="F18" t="s">
-        <v>137</v>
-      </c>
       <c r="I18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
       </c>
       <c r="C19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" t="s">
         <v>139</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>140</v>
       </c>
-      <c r="F19" t="s">
-        <v>141</v>
-      </c>
       <c r="I19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
       <c r="C20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" t="s">
         <v>143</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>144</v>
       </c>
-      <c r="F20" t="s">
+      <c r="I20" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>145</v>
-      </c>
-      <c r="I20" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>146</v>
       </c>
       <c r="B21" t="s">
         <v>71</v>
       </c>
       <c r="C21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" t="s">
         <v>147</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>148</v>
       </c>
-      <c r="F21" t="s">
-        <v>82</v>
-      </c>
-      <c r="G21" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -2928,111 +2919,117 @@
       <c r="C22" t="s">
         <v>150</v>
       </c>
-      <c r="E22" t="s">
+      <c r="D22" t="s">
         <v>151</v>
       </c>
       <c r="F22" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="G22" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s">
         <v>71</v>
       </c>
       <c r="C23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" t="s">
         <v>154</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>155</v>
       </c>
-      <c r="F23" t="s">
-        <v>156</v>
-      </c>
       <c r="I23" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s">
         <v>71</v>
       </c>
       <c r="C24" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" t="s">
         <v>158</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>159</v>
       </c>
-      <c r="F24" t="s">
-        <v>160</v>
-      </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
         <v>71</v>
       </c>
       <c r="C25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" t="s">
         <v>162</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>163</v>
       </c>
-      <c r="F25" t="s">
-        <v>164</v>
-      </c>
       <c r="I25" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
         <v>71</v>
       </c>
       <c r="C26" t="s">
+        <v>165</v>
+      </c>
+      <c r="D26" t="s">
         <v>166</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>167</v>
       </c>
-      <c r="F26" t="s">
-        <v>168</v>
-      </c>
       <c r="I26" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
         <v>71</v>
       </c>
       <c r="C27" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" t="s">
         <v>171</v>
       </c>
-      <c r="E27" t="s">
+      <c r="I27" t="s">
         <v>172</v>
-      </c>
-      <c r="I27" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -3045,31 +3042,31 @@
       <c r="C28" t="s">
         <v>174</v>
       </c>
-      <c r="E28" t="s">
+      <c r="D28" t="s">
         <v>175</v>
       </c>
-      <c r="F28" t="s">
-        <v>176</v>
-      </c>
       <c r="I28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B29" t="s">
         <v>71</v>
       </c>
       <c r="C29" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" t="s">
         <v>178</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>179</v>
       </c>
       <c r="I29" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -3082,31 +3079,31 @@
       <c r="C30" t="s">
         <v>181</v>
       </c>
-      <c r="E30" t="s">
+      <c r="D30" t="s">
         <v>182</v>
       </c>
-      <c r="F30" t="s">
-        <v>183</v>
-      </c>
       <c r="I30" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
         <v>71</v>
       </c>
       <c r="C31" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" t="s">
         <v>185</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>186</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -3119,71 +3116,71 @@
       <c r="C32" t="s">
         <v>188</v>
       </c>
-      <c r="E32" t="s">
+      <c r="D32" t="s">
         <v>189</v>
       </c>
-      <c r="F32" t="s">
-        <v>190</v>
-      </c>
       <c r="I32" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s">
         <v>71</v>
       </c>
       <c r="C33" t="s">
+        <v>191</v>
+      </c>
+      <c r="D33" t="s">
         <v>192</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>193</v>
       </c>
-      <c r="F33" t="s">
-        <v>194</v>
-      </c>
       <c r="I33" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
         <v>71</v>
       </c>
       <c r="C34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" t="s">
         <v>196</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>197</v>
       </c>
-      <c r="F34" t="s">
-        <v>198</v>
-      </c>
       <c r="I34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
         <v>71</v>
       </c>
       <c r="C35" t="s">
+        <v>199</v>
+      </c>
+      <c r="D35" t="s">
         <v>200</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>201</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -3196,11 +3193,11 @@
       <c r="C36" t="s">
         <v>203</v>
       </c>
-      <c r="E36" t="s">
+      <c r="D36" t="s">
         <v>204</v>
       </c>
       <c r="I36" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -3213,11 +3210,11 @@
       <c r="C37" t="s">
         <v>206</v>
       </c>
-      <c r="E37" t="s">
+      <c r="D37" t="s">
         <v>207</v>
       </c>
       <c r="I37" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -3230,28 +3227,28 @@
       <c r="C38" t="s">
         <v>209</v>
       </c>
-      <c r="E38" t="s">
+      <c r="D38" t="s">
         <v>210</v>
       </c>
       <c r="I38" t="s">
-        <v>211</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
         <v>71</v>
       </c>
       <c r="C39" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" t="s">
         <v>213</v>
       </c>
-      <c r="E39" t="s">
+      <c r="I39" t="s">
         <v>214</v>
-      </c>
-      <c r="I39" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -3264,167 +3261,170 @@
       <c r="C40" t="s">
         <v>216</v>
       </c>
-      <c r="E40" t="s">
+      <c r="D40" t="s">
         <v>217</v>
       </c>
-      <c r="F40" t="s">
-        <v>218</v>
-      </c>
       <c r="I40" t="s">
-        <v>86</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
         <v>71</v>
       </c>
       <c r="C41" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" t="s">
         <v>220</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>221</v>
       </c>
-      <c r="F41" t="s">
-        <v>222</v>
-      </c>
       <c r="I41" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B42" t="s">
         <v>71</v>
       </c>
       <c r="C42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D42" t="s">
         <v>224</v>
       </c>
-      <c r="E42" t="s">
+      <c r="I42" t="s">
         <v>225</v>
-      </c>
-      <c r="I42" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s">
         <v>71</v>
       </c>
       <c r="C43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" t="s">
         <v>228</v>
       </c>
-      <c r="E43" t="s">
-        <v>229</v>
-      </c>
       <c r="I43" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B44" t="s">
         <v>71</v>
       </c>
       <c r="C44" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" t="s">
         <v>231</v>
       </c>
-      <c r="E44" t="s">
-        <v>232</v>
-      </c>
       <c r="I44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B45" t="s">
         <v>71</v>
       </c>
       <c r="C45" t="s">
+        <v>233</v>
+      </c>
+      <c r="D45" t="s">
         <v>234</v>
       </c>
-      <c r="E45" t="s">
-        <v>235</v>
-      </c>
       <c r="I45" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B46" t="s">
         <v>71</v>
       </c>
       <c r="C46" t="s">
+        <v>236</v>
+      </c>
+      <c r="D46" t="s">
         <v>237</v>
       </c>
-      <c r="E46" t="s">
-        <v>238</v>
-      </c>
       <c r="I46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B47" t="s">
         <v>71</v>
       </c>
       <c r="C47" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" t="s">
         <v>240</v>
       </c>
-      <c r="E47" t="s">
-        <v>241</v>
-      </c>
       <c r="I47" t="s">
-        <v>242</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B48" t="s">
         <v>71</v>
       </c>
       <c r="C48" t="s">
+        <v>242</v>
+      </c>
+      <c r="D48" t="s">
+        <v>243</v>
+      </c>
+      <c r="I48" t="s">
         <v>244</v>
       </c>
-      <c r="E48" t="s">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>245</v>
-      </c>
-      <c r="I48" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>246</v>
       </c>
       <c r="B49" t="s">
         <v>71</v>
       </c>
       <c r="C49" t="s">
+        <v>246</v>
+      </c>
+      <c r="D49" t="s">
         <v>247</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>248</v>
+      </c>
+      <c r="I49" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3702,7 +3702,7 @@
         <v>297</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3742,7 +3742,7 @@
         <v>304</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s">
         <v>306</v>
@@ -3837,7 +3837,7 @@
         <v>316</v>
       </c>
       <c r="G2" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3903,7 +3903,7 @@
         <v>328</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H5" t="s">
         <v>329</v>
@@ -3926,10 +3926,10 @@
         <v>332</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -3949,7 +3949,7 @@
         <v>335</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
         <v>336</v>
@@ -3978,7 +3978,7 @@
         <v>316</v>
       </c>
       <c r="G8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,7 +3998,7 @@
         <v>343</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -4021,7 +4021,7 @@
         <v>347</v>
       </c>
       <c r="G10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
         <v>266</v>
@@ -4047,7 +4047,7 @@
         <v>351</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4067,10 +4067,10 @@
         <v>354</v>
       </c>
       <c r="F12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4090,7 +4090,7 @@
         <v>357</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
         <v>336</v>
@@ -4119,7 +4119,7 @@
         <v>362</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
         <v>336</v>
@@ -4145,7 +4145,7 @@
         <v>366</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
         <v>336</v>
@@ -4171,7 +4171,7 @@
         <v>370</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -4191,7 +4191,7 @@
         <v>373</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s">
         <v>336</v>
@@ -4240,7 +4240,7 @@
         <v>382</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s">
         <v>336</v>
@@ -4266,7 +4266,7 @@
         <v>386</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -4286,7 +4286,7 @@
         <v>389</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
         <v>336</v>
@@ -4335,7 +4335,7 @@
         <v>398</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
         <v>399</v>
@@ -4358,7 +4358,7 @@
         <v>402</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
         <v>351</v>
@@ -4404,7 +4404,7 @@
         <v>408</v>
       </c>
       <c r="F26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s">
         <v>336</v>
@@ -4430,7 +4430,7 @@
         <v>412</v>
       </c>
       <c r="F27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s">
         <v>413</v>
@@ -4453,7 +4453,7 @@
         <v>416</v>
       </c>
       <c r="F28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s">
         <v>336</v>
@@ -4482,7 +4482,7 @@
         <v>421</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s">
         <v>336</v>
@@ -4505,7 +4505,7 @@
         <v>424</v>
       </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s">
         <v>336</v>
@@ -4577,10 +4577,10 @@
         <v>438</v>
       </c>
       <c r="F33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -4600,7 +4600,7 @@
         <v>441</v>
       </c>
       <c r="F34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s">
         <v>413</v>
@@ -4623,7 +4623,7 @@
         <v>444</v>
       </c>
       <c r="F35" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -4666,10 +4666,10 @@
         <v>451</v>
       </c>
       <c r="F37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s">
-        <v>211</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -4689,7 +4689,7 @@
         <v>454</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s">
         <v>325</v>
@@ -4712,7 +4712,7 @@
         <v>457</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s">
         <v>336</v>
@@ -4738,7 +4738,7 @@
         <v>461</v>
       </c>
       <c r="F40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s">
         <v>336</v>
@@ -4767,7 +4767,7 @@
         <v>466</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s">
         <v>336</v>
@@ -4793,7 +4793,7 @@
         <v>470</v>
       </c>
       <c r="F42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s">
         <v>336</v>
@@ -4819,7 +4819,7 @@
         <v>474</v>
       </c>
       <c r="F43" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s">
         <v>475</v>
@@ -4842,7 +4842,7 @@
         <v>478</v>
       </c>
       <c r="F44" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s">
         <v>336</v>
@@ -4868,7 +4868,7 @@
         <v>482</v>
       </c>
       <c r="F45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s">
         <v>336</v>
@@ -4894,7 +4894,7 @@
         <v>486</v>
       </c>
       <c r="F46" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s">
         <v>336</v>
@@ -4940,7 +4940,7 @@
         <v>493</v>
       </c>
       <c r="F48" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s">
         <v>336</v>
@@ -4969,7 +4969,7 @@
         <v>498</v>
       </c>
       <c r="F49" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s">
         <v>336</v>
@@ -4995,7 +4995,7 @@
         <v>502</v>
       </c>
       <c r="F50" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s">
         <v>336</v>
@@ -5024,7 +5024,7 @@
         <v>507</v>
       </c>
       <c r="F51" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s">
         <v>336</v>
@@ -5050,7 +5050,7 @@
         <v>511</v>
       </c>
       <c r="F52" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s">
         <v>512</v>
@@ -5073,7 +5073,7 @@
         <v>515</v>
       </c>
       <c r="F53" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s">
         <v>336</v>
@@ -5099,7 +5099,7 @@
         <v>519</v>
       </c>
       <c r="F54" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s">
         <v>336</v>
@@ -5125,10 +5125,10 @@
         <v>523</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
